--- a/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
+++ b/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A53D06-F578-4010-B540-120243886255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD6924-6A73-427B-A691-61E12DB36AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>StoryID</t>
   </si>
@@ -1025,9 +1025,7 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1039,9 +1037,7 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>

--- a/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
+++ b/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD6924-6A73-427B-A691-61E12DB36AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACD3051-DB9A-42EE-9FC2-52D6BF666069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -68,10 +68,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>right</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -286,6 +282,10 @@
       </rPr>
       <t>6</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -779,85 +779,85 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="K1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -968,10 +968,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
@@ -985,20 +985,20 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1009,16 +1009,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
+++ b/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACD3051-DB9A-42EE-9FC2-52D6BF666069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646ADFC5-5C5B-4F05-A324-BDF9DFF2CD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="3645" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>LineIndex</t>
   </si>
@@ -76,64 +62,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>clinic</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>current_scene</t>
@@ -288,16 +223,101 @@
     <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -311,7 +331,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -332,20 +352,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -366,8 +378,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,20 +416,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -426,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -449,33 +485,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -753,184 +806,211 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" customWidth="1"/>
+    <col min="14" max="14" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="20" customFormat="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="36">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D2" s="12">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="54" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="L3" s="16"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="13"/>
+      <c r="T2" s="21"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="11"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{771C29DE-CAD8-449F-94BA-64B3300E49D1}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{0B2E8918-9249-46B9-A361-A23FCDE4EFBB}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{4E0D2EEE-9486-4268-B930-C4690E29B225}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{687ADB94-942D-427F-A8F3-A9139B2EB3AE}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{EC52F775-5A68-4D24-8978-C94F65C3C178}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -938,90 +1018,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1033,7 +1113,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>

--- a/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
+++ b/DataTables/DetailText/剧情/017_01杨善泉肾气不固.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646ADFC5-5C5B-4F05-A324-BDF9DFF2CD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9158BA-5306-4036-B3B8-0B4F8FF4289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="3645" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19050" yWindow="6090" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>LineIndex</t>
   </si>
@@ -308,6 +319,10 @@
     <t>奖励心得</t>
     <phoneticPr fontId="10"/>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -317,7 +332,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -331,7 +346,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -352,7 +367,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -462,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -526,9 +541,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -807,25 +825,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.33203125" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
+    <col min="14" max="14" width="8.75" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="37" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="13" t="s">
         <v>26</v>
       </c>
@@ -1017,21 +1035,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1056,8 +1074,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1080,8 +1101,9 @@
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1100,8 +1122,9 @@
       <c r="H3" s="12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1112,8 +1135,9 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1124,6 +1148,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
